--- a/excel_files/12.xlsx
+++ b/excel_files/12.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,10 +458,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -818,384 +818,6 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>181-190</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>270-260</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>191-200</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>260-250</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>201-210</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>250-240</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>211-220</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>240-230</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>221-230</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>230-220</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>231-240</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>220-210</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>241-250</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>210-200</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>251-260</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>200-190</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>261-270</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>190-180</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>271-280</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>180-170</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>281-290</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>170-160</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>291-300</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>160-150</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>301-310</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>150-140</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>311-320</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>140-130</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>321-330</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>130-120</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>331-340</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>120-110</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>341-350</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>110-100</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>351-360</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>100-90</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
         <v>0</v>
       </c>
     </row>
